--- a/data/trans_orig/IP38E_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP38E_2023-Provincia-trans_orig.xlsx
@@ -730,7 +730,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15025</t>
+          <t>15177</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -745,7 +745,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>77,74%</t>
+          <t>78,52%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22904</t>
+          <t>21946</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>80,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>39445</t>
+          <t>39907</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>45875</t>
+          <t>45825</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>85,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,41%</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>4151</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4333</t>
+          <t>5291</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>690</t>
+          <t>740</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7120</t>
+          <t>6658</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>14,3%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17787</t>
+          <t>17119</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24763</t>
+          <t>24702</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>62,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>27188</t>
+          <t>26665</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34921</t>
+          <t>34924</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>73,17%</t>
+          <t>71,77%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>47481</t>
+          <t>47645</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>58139</t>
+          <t>58290</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>73,43%</t>
+          <t>73,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>90,14%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2746</t>
+          <t>2807</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9722</t>
+          <t>10390</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>37,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2234</t>
+          <t>2231</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9967</t>
+          <t>10490</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6525</t>
+          <t>6374</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>17183</t>
+          <t>17019</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,32%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11074</t>
+          <t>11497</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17135</t>
+          <t>17158</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>59,12%</t>
+          <t>61,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15000</t>
+          <t>15390</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20161</t>
+          <t>20168</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>70,65%</t>
+          <t>72,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29098</t>
+          <t>29043</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>36307</t>
+          <t>36279</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>72,82%</t>
+          <t>72,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>90,78%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1595</t>
+          <t>1572</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7656</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>38,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1071</t>
+          <t>1064</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6232</t>
+          <t>5842</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3655</t>
+          <t>3683</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>10864</t>
+          <t>10919</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>27,32%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11230</t>
+          <t>10918</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17018</t>
+          <t>17008</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>64,07%</t>
+          <t>62,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>30889</t>
+          <t>31619</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>37056</t>
+          <t>37069</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>84,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,79%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>508</t>
+          <t>518</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6296</t>
+          <t>6608</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>37,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>465</t>
+          <t>452</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6632</t>
+          <t>5902</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>15,73%</t>
         </is>
       </c>
     </row>
@@ -2137,7 +2137,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3858</t>
+          <t>3847</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>55,33%</t>
+          <t>55,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9735</t>
+          <t>9771</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>75,5%</t>
+          <t>75,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3114</t>
+          <t>3125</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>44,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3158</t>
+          <t>3122</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,22%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13267</t>
+          <t>13668</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18481</t>
+          <t>18719</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>66,38%</t>
+          <t>68,38%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14963</t>
+          <t>15477</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24026</t>
+          <t>24060</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>57,84%</t>
+          <t>59,83%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>32034</t>
+          <t>30958</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>41462</t>
+          <t>41310</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>69,85%</t>
+          <t>67,51%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,08%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1507</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6721</t>
+          <t>6320</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1845</t>
+          <t>1811</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10908</t>
+          <t>10394</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>40,17%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4397</t>
+          <t>4549</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>13825</t>
+          <t>14901</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>32,49%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>21667</t>
+          <t>19458</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>33397</t>
+          <t>33264</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>59,62%</t>
+          <t>53,55%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>36033</t>
+          <t>36039</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>44985</t>
+          <t>44854</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>77,1%</t>
+          <t>77,11%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>61213</t>
+          <t>61075</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>76810</t>
+          <t>76393</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>73,69%</t>
+          <t>73,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>91,96%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2942</t>
+          <t>3075</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>14672</t>
+          <t>16881</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>40,38%</t>
+          <t>46,45%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1749</t>
+          <t>1880</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>10701</t>
+          <t>10695</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6263</t>
+          <t>6680</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>21860</t>
+          <t>21998</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>26,48%</t>
         </is>
       </c>
     </row>
@@ -3131,12 +3131,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>41690</t>
+          <t>41665</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>49111</t>
+          <t>49271</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>83,03%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>43618</t>
+          <t>43210</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>51120</t>
+          <t>50967</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>82,66%</t>
+          <t>81,89%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>89210</t>
+          <t>88382</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>99021</t>
+          <t>99013</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,18%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1068</t>
+          <t>908</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>8489</t>
+          <t>8514</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1647</t>
+          <t>1800</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>9149</t>
+          <t>9557</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3925</t>
+          <t>3933</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>13736</t>
+          <t>14564</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>14,15%</t>
         </is>
       </c>
     </row>
@@ -3474,12 +3474,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>157227</t>
+          <t>157476</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>176039</t>
+          <t>176004</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>80,54%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>202410</t>
+          <t>202587</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>220819</t>
+          <t>220907</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>85,06%</t>
+          <t>85,13%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>368685</t>
+          <t>368776</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>394305</t>
+          <t>392975</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>90,66%</t>
         </is>
       </c>
     </row>
@@ -3587,12 +3587,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>19480</t>
+          <t>19515</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>38292</t>
+          <t>38043</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>17144</t>
+          <t>17056</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>35553</t>
+          <t>35376</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>39177</t>
+          <t>40507</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>64797</t>
+          <t>64706</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3672,12 +3672,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>14,93%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP38E_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP38E_2023-Provincia-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,74 +720,74 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>20095</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>17549</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>21295</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>94,37%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>82,41%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>18040</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>15177</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>19328</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>93,33%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>78,52%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>12938</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>10631</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>14073</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>91,94%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>75,54%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>25788</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>21946</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>27237</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>94,68%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>80,57%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>55</t>
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>43828</t>
+          <t>33033</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>39907</t>
+          <t>29869</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>45825</t>
+          <t>34688</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>84,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,08%</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4151</t>
+          <t>3746</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>1135</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5291</t>
+          <t>3442</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>2737</t>
+          <t>2335</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>740</t>
+          <t>680</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6658</t>
+          <t>5499</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>15,55%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>21295</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>21295</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>21295</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>19328</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>19328</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>19328</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>27237</t>
+          <t>14073</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>27237</t>
+          <t>14073</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>27237</t>
+          <t>14073</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>46565</t>
+          <t>35368</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>46565</t>
+          <t>35368</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>46565</t>
+          <t>35368</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>29125</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>24503</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>31983</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>85,84%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>72,22%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>94,26%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>21818</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>17119</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>24702</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>79,31%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>62,23%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>89,8%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>31987</t>
+          <t>21726</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26665</t>
+          <t>17320</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34924</t>
+          <t>24793</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>86,09%</t>
+          <t>78,79%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>71,77%</t>
+          <t>62,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>53805</t>
+          <t>50851</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>47645</t>
+          <t>44102</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>58290</t>
+          <t>55333</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>82,68%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>73,68%</t>
+          <t>71,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>89,97%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4804</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1946</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>9426</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>14,16%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>5,74%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>27,78%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>5691</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>2807</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>10390</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>20,69%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>10,2%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>37,77%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>5848</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2231</t>
+          <t>2781</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10490</t>
+          <t>10254</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>37,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>10859</t>
+          <t>10652</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6374</t>
+          <t>6170</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>17019</t>
+          <t>17401</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>28,29%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>33929</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>33929</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>33929</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>27509</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>27509</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>27509</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>37155</t>
+          <t>27574</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>37155</t>
+          <t>27574</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>37155</t>
+          <t>27574</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>64664</t>
+          <t>61503</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>64664</t>
+          <t>61503</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>64664</t>
+          <t>61503</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>15887</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>13216</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>17431</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>86,27%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>71,77%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>94,66%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>14974</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>11497</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>17158</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>79,95%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>61,38%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>91,61%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>18356</t>
+          <t>14379</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15390</t>
+          <t>11144</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20168</t>
+          <t>16687</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>78,95%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>72,49%</t>
+          <t>61,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>33330</t>
+          <t>30265</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29043</t>
+          <t>26265</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>36279</t>
+          <t>33444</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>83,4%</t>
+          <t>82,63%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>72,68%</t>
+          <t>71,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>91,31%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3756</t>
+          <t>2527</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1572</t>
+          <t>983</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>5198</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,62%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2876</t>
+          <t>3833</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1064</t>
+          <t>1525</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5842</t>
+          <t>7068</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>38,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>6632</t>
+          <t>6361</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3683</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>10919</t>
+          <t>10361</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>28,29%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>18414</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>18414</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>18414</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>18730</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>18730</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>18730</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>21232</t>
+          <t>18212</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>21232</t>
+          <t>18212</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>21232</t>
+          <t>18212</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>39962</t>
+          <t>36626</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>39962</t>
+          <t>36626</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>39962</t>
+          <t>36626</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>18985</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>15398</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>10918</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>17008</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>87,86%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>62,3%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>97,04%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>19995</t>
+          <t>15424</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10502</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>17201</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>59,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>35393</t>
+          <t>34409</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>31619</t>
+          <t>29537</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>37069</t>
+          <t>36201</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>80,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>99,02%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>2128</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>518</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>6608</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>12,14%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>2,96%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>37,7%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2149</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>372</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7071</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>40,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>2128</t>
+          <t>2149</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>452</t>
+          <t>357</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5902</t>
+          <t>7021</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>19,21%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>18985</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>18985</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>18985</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>17526</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>17526</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>17526</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>19995</t>
+          <t>17573</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>19995</t>
+          <t>17573</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>19995</t>
+          <t>17573</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>37521</t>
+          <t>36558</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>37521</t>
+          <t>36558</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>37521</t>
+          <t>36558</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,74 +2092,74 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>6238</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>4196</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>6889</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>90,55%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>60,91%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>5921</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>6261</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>6316</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>3847</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>6972</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>90,59%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>55,18%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>23</t>
@@ -2167,27 +2167,27 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>12237</t>
+          <t>12498</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9771</t>
+          <t>9955</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12893</t>
+          <t>13149</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>75,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2205,107 +2205,107 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>651</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>2715</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>9,45%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>39,4%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>651</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>3125</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>9,41%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>3194</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>4,95%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>44,82%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>3122</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>5,09%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,29%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5921</t>
+          <t>6889</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5921</t>
+          <t>6889</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5921</t>
+          <t>6889</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>6972</t>
+          <t>6261</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6972</t>
+          <t>6261</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6972</t>
+          <t>6261</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>12893</t>
+          <t>13149</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>12893</t>
+          <t>13149</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>12893</t>
+          <t>13149</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2435,72 +2435,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>18800</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>14075</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>21316</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>81,47%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>61,0%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>92,38%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>16568</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>13668</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>18719</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>82,89%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>68,38%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>93,65%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>21139</t>
+          <t>16264</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15477</t>
+          <t>13181</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24060</t>
+          <t>18547</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>81,71%</t>
+          <t>82,11%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>66,55%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>37707</t>
+          <t>35064</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>30958</t>
+          <t>29078</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>41310</t>
+          <t>38531</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>82,22%</t>
+          <t>81,77%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>67,51%</t>
+          <t>67,81%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>89,85%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>3420</t>
+          <t>4276</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1760</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6320</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>39,0%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>4732</t>
+          <t>3544</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1811</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10394</t>
+          <t>6627</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>33,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>8152</t>
+          <t>7820</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4549</t>
+          <t>4353</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>14901</t>
+          <t>13806</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,19%</t>
         </is>
       </c>
     </row>
@@ -2661,57 +2661,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>23076</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>23076</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>23076</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>19988</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>19988</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>19988</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>25871</t>
+          <t>19808</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>25871</t>
+          <t>19808</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>25871</t>
+          <t>19808</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>45859</t>
+          <t>42884</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>45859</t>
+          <t>42884</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>45859</t>
+          <t>42884</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>39787</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>34648</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>43172</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>88,9%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>77,42%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>96,46%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>28952</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>19458</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>33264</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>79,67%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>53,55%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>91,54%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>41776</t>
+          <t>29785</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>36039</t>
+          <t>24997</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>44854</t>
+          <t>32634</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>77,11%</t>
+          <t>71,83%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>70727</t>
+          <t>69572</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>61075</t>
+          <t>61865</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>76393</t>
+          <t>73777</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>87,45%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>73,52%</t>
+          <t>77,76%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>92,73%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>4969</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>1584</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>10108</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>11,1%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>3,54%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>22,58%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>7387</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>3075</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>16881</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>20,33%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>8,46%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>46,45%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>5016</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1880</t>
+          <t>2167</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>10695</t>
+          <t>9804</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>12346</t>
+          <t>9985</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6680</t>
+          <t>5780</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>21998</t>
+          <t>17692</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>22,24%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>44756</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>44756</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>44756</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>36339</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>36339</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>36339</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>46734</t>
+          <t>34801</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>46734</t>
+          <t>34801</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>46734</t>
+          <t>34801</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>83073</t>
+          <t>79557</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>83073</t>
+          <t>79557</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>83073</t>
+          <t>79557</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3121,72 +3121,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>48770</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>43813</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>51448</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>91,26%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>81,98%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>96,27%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>46577</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>41665</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>49271</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>92,82%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>83,03%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>98,19%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>48278</t>
+          <t>50221</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>43210</t>
+          <t>44652</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>50967</t>
+          <t>53139</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>82,32%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>94855</t>
+          <t>98991</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>88382</t>
+          <t>92774</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>99013</t>
+          <t>103363</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>86,15%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>95,99%</t>
         </is>
       </c>
     </row>
@@ -3234,72 +3234,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>4673</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>1995</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>9630</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>8,74%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>3,73%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>18,02%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>3602</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>908</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>8514</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>7,18%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>1,81%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>16,97%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>4489</t>
+          <t>4019</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1800</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>9557</t>
+          <t>9588</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>8091</t>
+          <t>8692</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3933</t>
+          <t>4320</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>14564</t>
+          <t>14909</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>13,85%</t>
         </is>
       </c>
     </row>
@@ -3347,57 +3347,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>53443</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>53443</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>53443</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>50179</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>50179</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>50179</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>52767</t>
+          <t>54240</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>52767</t>
+          <t>54240</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>52767</t>
+          <t>54240</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>102946</t>
+          <t>107683</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>102946</t>
+          <t>107683</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>102946</t>
+          <t>107683</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3464,72 +3464,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>197686</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>187060</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>203898</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>89,54%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>84,72%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>92,35%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>247</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>168247</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>157476</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>176004</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>86,05%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>80,54%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>90,02%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>285</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>213635</t>
+          <t>166998</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>202587</t>
+          <t>157881</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>220907</t>
+          <t>174815</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>82,0%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>381882</t>
+          <t>364684</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>368776</t>
+          <t>352379</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>392975</t>
+          <t>376801</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>85,25%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>91,16%</t>
         </is>
       </c>
     </row>
@@ -3577,72 +3577,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>23100</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>16888</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>33726</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>10,46%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>7,65%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>15,28%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>27272</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>19515</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>38043</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>13,95%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>9,98%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>19,46%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>24328</t>
+          <t>25544</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>17056</t>
+          <t>17727</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>35376</t>
+          <t>34661</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,32 +3652,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>51600</t>
+          <t>48644</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>40507</t>
+          <t>36527</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>64706</t>
+          <t>60949</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,75%</t>
         </is>
       </c>
     </row>
@@ -3690,57 +3690,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>318</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>220786</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>220786</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>220786</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>283</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>195519</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>195519</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>195519</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>318</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>237963</t>
+          <t>192542</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>237963</t>
+          <t>192542</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>237963</t>
+          <t>192542</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>433482</t>
+          <t>413328</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>433482</t>
+          <t>413328</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>433482</t>
+          <t>413328</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
